--- a/artifacts/ClinicOS_Pilot_Tracker.xlsx
+++ b/artifacts/ClinicOS_Pilot_Tracker.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Dr S. Ghosh</t>
   </si>
   <si>
-    <t xml:space="preserve">Krishnanagar, near bus stand</t>
+    <t xml:space="preserve">Solo clinic, town centre</t>
   </si>
   <si>
     <t xml:space="preserve">Y</t>
